--- a/input/통합_강의계획서_입력양식.xlsx
+++ b/input/통합_강의계획서_입력양식.xlsx
@@ -12,6 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="강좌2" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="강좌3" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="강좌4" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="선택목록" sheetId="7" state="hidden" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -593,7 +594,6 @@
       <c r="D1" s="32" t="n"/>
       <c r="E1" s="33" t="n"/>
     </row>
-    <row r="2"/>
     <row r="3" ht="36" customHeight="1">
       <c r="A3" s="1" t="inlineStr">
         <is>
@@ -1037,7 +1037,6 @@
       <c r="D19" s="32" t="n"/>
       <c r="E19" s="33" t="n"/>
     </row>
-    <row r="20"/>
     <row r="21" ht="24" customHeight="1">
       <c r="A21" s="36" t="inlineStr">
         <is>
@@ -1156,7 +1155,6 @@
       <c r="D28" s="32" t="n"/>
       <c r="E28" s="33" t="n"/>
     </row>
-    <row r="29"/>
     <row r="30" ht="21.95" customHeight="1">
       <c r="A30" s="39" t="inlineStr">
         <is>
@@ -1179,7 +1177,6 @@
       <c r="D31" s="32" t="n"/>
       <c r="E31" s="33" t="n"/>
     </row>
-    <row r="32"/>
     <row r="33" ht="24" customHeight="1">
       <c r="A33" s="36" t="inlineStr">
         <is>
@@ -1637,7 +1634,6 @@
       <c r="D19" s="32" t="n"/>
       <c r="E19" s="33" t="n"/>
     </row>
-    <row r="20"/>
     <row r="21" ht="24" customHeight="1">
       <c r="A21" s="36" t="inlineStr">
         <is>
@@ -1726,7 +1722,6 @@
       <c r="D28" s="32" t="n"/>
       <c r="E28" s="33" t="n"/>
     </row>
-    <row r="29"/>
     <row r="30" ht="21.95" customHeight="1">
       <c r="A30" s="39" t="inlineStr">
         <is>
@@ -1749,7 +1744,6 @@
       <c r="D31" s="32" t="n"/>
       <c r="E31" s="33" t="n"/>
     </row>
-    <row r="32"/>
     <row r="33" ht="24" customHeight="1">
       <c r="A33" s="36" t="inlineStr">
         <is>
@@ -1904,6 +1898,17 @@
     <mergeCell ref="B10:E10"/>
     <mergeCell ref="B28:E28"/>
   </mergeCells>
+  <dataValidations count="3">
+    <dataValidation sqref="B5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="입력 값 확인" error="드롭다운 목록에서 선택해 주세요." promptTitle="강좌 유형" prompt="드롭다운에서 선택" type="list">
+      <formula1>'선택목록'!$A$2:$A$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="B6" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="입력 값 확인" error="드롭다운 목록에서 선택해 주세요." promptTitle="학년" prompt="드롭다운에서 선택" type="list">
+      <formula1>'선택목록'!$B$2:$B$5</formula1>
+    </dataValidation>
+    <dataValidation sqref="B9" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="입력 값 확인" error="드롭다운 목록에서 선택해 주세요." promptTitle="강의형태" prompt="드롭다운에서 선택" type="list">
+      <formula1>'선택목록'!$C$2:$C$3</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2123,7 +2128,6 @@
       <c r="D19" s="32" t="n"/>
       <c r="E19" s="33" t="n"/>
     </row>
-    <row r="20"/>
     <row r="21" ht="24" customHeight="1">
       <c r="A21" s="36" t="inlineStr">
         <is>
@@ -2212,7 +2216,6 @@
       <c r="D28" s="32" t="n"/>
       <c r="E28" s="33" t="n"/>
     </row>
-    <row r="29"/>
     <row r="30" ht="21.95" customHeight="1">
       <c r="A30" s="39" t="inlineStr">
         <is>
@@ -2235,7 +2238,6 @@
       <c r="D31" s="32" t="n"/>
       <c r="E31" s="33" t="n"/>
     </row>
-    <row r="32"/>
     <row r="33" ht="24" customHeight="1">
       <c r="A33" s="36" t="inlineStr">
         <is>
@@ -2390,6 +2392,17 @@
     <mergeCell ref="B10:E10"/>
     <mergeCell ref="B28:E28"/>
   </mergeCells>
+  <dataValidations count="3">
+    <dataValidation sqref="B5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="입력 값 확인" error="드롭다운 목록에서 선택해 주세요." promptTitle="강좌 유형" prompt="드롭다운에서 선택" type="list">
+      <formula1>'선택목록'!$A$2:$A$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="B6" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="입력 값 확인" error="드롭다운 목록에서 선택해 주세요." promptTitle="학년" prompt="드롭다운에서 선택" type="list">
+      <formula1>'선택목록'!$B$2:$B$5</formula1>
+    </dataValidation>
+    <dataValidation sqref="B9" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="입력 값 확인" error="드롭다운 목록에서 선택해 주세요." promptTitle="강의형태" prompt="드롭다운에서 선택" type="list">
+      <formula1>'선택목록'!$C$2:$C$3</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2609,7 +2622,6 @@
       <c r="D19" s="32" t="n"/>
       <c r="E19" s="33" t="n"/>
     </row>
-    <row r="20"/>
     <row r="21" ht="24" customHeight="1">
       <c r="A21" s="36" t="inlineStr">
         <is>
@@ -2698,7 +2710,6 @@
       <c r="D28" s="32" t="n"/>
       <c r="E28" s="33" t="n"/>
     </row>
-    <row r="29"/>
     <row r="30" ht="21.95" customHeight="1">
       <c r="A30" s="39" t="inlineStr">
         <is>
@@ -2721,7 +2732,6 @@
       <c r="D31" s="32" t="n"/>
       <c r="E31" s="33" t="n"/>
     </row>
-    <row r="32"/>
     <row r="33" ht="24" customHeight="1">
       <c r="A33" s="36" t="inlineStr">
         <is>
@@ -2876,6 +2886,17 @@
     <mergeCell ref="B10:E10"/>
     <mergeCell ref="B28:E28"/>
   </mergeCells>
+  <dataValidations count="3">
+    <dataValidation sqref="B5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="입력 값 확인" error="드롭다운 목록에서 선택해 주세요." promptTitle="강좌 유형" prompt="드롭다운에서 선택" type="list">
+      <formula1>'선택목록'!$A$2:$A$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="B6" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="입력 값 확인" error="드롭다운 목록에서 선택해 주세요." promptTitle="학년" prompt="드롭다운에서 선택" type="list">
+      <formula1>'선택목록'!$B$2:$B$5</formula1>
+    </dataValidation>
+    <dataValidation sqref="B9" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="입력 값 확인" error="드롭다운 목록에서 선택해 주세요." promptTitle="강의형태" prompt="드롭다운에서 선택" type="list">
+      <formula1>'선택목록'!$C$2:$C$3</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3095,7 +3116,6 @@
       <c r="D19" s="32" t="n"/>
       <c r="E19" s="33" t="n"/>
     </row>
-    <row r="20"/>
     <row r="21" ht="24" customHeight="1">
       <c r="A21" s="36" t="inlineStr">
         <is>
@@ -3184,7 +3204,6 @@
       <c r="D28" s="32" t="n"/>
       <c r="E28" s="33" t="n"/>
     </row>
-    <row r="29"/>
     <row r="30" ht="21.95" customHeight="1">
       <c r="A30" s="39" t="inlineStr">
         <is>
@@ -3207,7 +3226,6 @@
       <c r="D31" s="32" t="n"/>
       <c r="E31" s="33" t="n"/>
     </row>
-    <row r="32"/>
     <row r="33" ht="24" customHeight="1">
       <c r="A33" s="36" t="inlineStr">
         <is>
@@ -3362,7 +3380,97 @@
     <mergeCell ref="B10:E10"/>
     <mergeCell ref="B28:E28"/>
   </mergeCells>
+  <dataValidations count="3">
+    <dataValidation sqref="B5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="입력 값 확인" error="드롭다운 목록에서 선택해 주세요." promptTitle="강좌 유형" prompt="드롭다운에서 선택" type="list">
+      <formula1>'선택목록'!$A$2:$A$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="B6" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="입력 값 확인" error="드롭다운 목록에서 선택해 주세요." promptTitle="학년" prompt="드롭다운에서 선택" type="list">
+      <formula1>'선택목록'!$B$2:$B$5</formula1>
+    </dataValidation>
+    <dataValidation sqref="B9" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="입력 값 확인" error="드롭다운 목록에서 선택해 주세요." promptTitle="강의형태" prompt="드롭다운에서 선택" type="list">
+      <formula1>'선택목록'!$C$2:$C$3</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>강좌유형</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>학년</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>강의형태</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>수능</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>중3</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>LIVE 강의</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>내신</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>고1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>현장 강의</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>고2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>고3, N수</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/input/통합_강의계획서_입력양식.xlsx
+++ b/input/통합_강의계획서_입력양식.xlsx
@@ -1898,7 +1898,7 @@
     <mergeCell ref="B10:E10"/>
     <mergeCell ref="B28:E28"/>
   </mergeCells>
-  <dataValidations count="3">
+  <dataValidations count="4">
     <dataValidation sqref="B5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="입력 값 확인" error="드롭다운 목록에서 선택해 주세요." promptTitle="강좌 유형" prompt="드롭다운에서 선택" type="list">
       <formula1>'선택목록'!$A$2:$A$3</formula1>
     </dataValidation>
@@ -1907,6 +1907,9 @@
     </dataValidation>
     <dataValidation sqref="B9" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="입력 값 확인" error="드롭다운 목록에서 선택해 주세요." promptTitle="강의형태" prompt="드롭다운에서 선택" type="list">
       <formula1>'선택목록'!$C$2:$C$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="B7" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="입력 값 확인" error="드롭다운 목록에서 과목을 선택해 주세요." promptTitle="과목" prompt="드롭다운에서 선택" type="list">
+      <formula1>'선택목록'!$D$2:$D$22</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2392,7 +2395,7 @@
     <mergeCell ref="B10:E10"/>
     <mergeCell ref="B28:E28"/>
   </mergeCells>
-  <dataValidations count="3">
+  <dataValidations count="4">
     <dataValidation sqref="B5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="입력 값 확인" error="드롭다운 목록에서 선택해 주세요." promptTitle="강좌 유형" prompt="드롭다운에서 선택" type="list">
       <formula1>'선택목록'!$A$2:$A$3</formula1>
     </dataValidation>
@@ -2401,6 +2404,9 @@
     </dataValidation>
     <dataValidation sqref="B9" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="입력 값 확인" error="드롭다운 목록에서 선택해 주세요." promptTitle="강의형태" prompt="드롭다운에서 선택" type="list">
       <formula1>'선택목록'!$C$2:$C$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="B7" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="입력 값 확인" error="드롭다운 목록에서 과목을 선택해 주세요." promptTitle="과목" prompt="드롭다운에서 선택" type="list">
+      <formula1>'선택목록'!$D$2:$D$22</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2886,7 +2892,7 @@
     <mergeCell ref="B10:E10"/>
     <mergeCell ref="B28:E28"/>
   </mergeCells>
-  <dataValidations count="3">
+  <dataValidations count="4">
     <dataValidation sqref="B5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="입력 값 확인" error="드롭다운 목록에서 선택해 주세요." promptTitle="강좌 유형" prompt="드롭다운에서 선택" type="list">
       <formula1>'선택목록'!$A$2:$A$3</formula1>
     </dataValidation>
@@ -2895,6 +2901,9 @@
     </dataValidation>
     <dataValidation sqref="B9" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="입력 값 확인" error="드롭다운 목록에서 선택해 주세요." promptTitle="강의형태" prompt="드롭다운에서 선택" type="list">
       <formula1>'선택목록'!$C$2:$C$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="B7" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="입력 값 확인" error="드롭다운 목록에서 과목을 선택해 주세요." promptTitle="과목" prompt="드롭다운에서 선택" type="list">
+      <formula1>'선택목록'!$D$2:$D$22</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3380,7 +3389,7 @@
     <mergeCell ref="B10:E10"/>
     <mergeCell ref="B28:E28"/>
   </mergeCells>
-  <dataValidations count="3">
+  <dataValidations count="4">
     <dataValidation sqref="B5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="입력 값 확인" error="드롭다운 목록에서 선택해 주세요." promptTitle="강좌 유형" prompt="드롭다운에서 선택" type="list">
       <formula1>'선택목록'!$A$2:$A$3</formula1>
     </dataValidation>
@@ -3389,6 +3398,9 @@
     </dataValidation>
     <dataValidation sqref="B9" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="입력 값 확인" error="드롭다운 목록에서 선택해 주세요." promptTitle="강의형태" prompt="드롭다운에서 선택" type="list">
       <formula1>'선택목록'!$C$2:$C$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="B7" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="입력 값 확인" error="드롭다운 목록에서 과목을 선택해 주세요." promptTitle="과목" prompt="드롭다운에서 선택" type="list">
+      <formula1>'선택목록'!$D$2:$D$22</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3402,7 +3414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3421,6 +3433,11 @@
           <t>강의형태</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>과목</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3438,6 +3455,11 @@
           <t>LIVE 강의</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>국어</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3455,6 +3477,11 @@
           <t>현장 강의</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>수학</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="B4" t="inlineStr">
@@ -3462,11 +3489,140 @@
           <t>고2</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>영어</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="B5" t="inlineStr">
         <is>
           <t>고3, N수</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>논술</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>수리논술</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>통합과학</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>물리</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>화학</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>생명과학</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>지구과학</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>통합사회</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>생활과윤리</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>윤리와사상</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>경제</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>정치와법</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>한국지리</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>세계지리</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>세계사</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>동아시아사</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>사회문화</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>한국사</t>
         </is>
       </c>
     </row>
